--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -25,10 +25,10 @@
     <t>Avg With Rate(USD/mt,VAT included)</t>
   </si>
   <si>
-    <t>106500</t>
+    <t>107000</t>
   </si>
   <si>
-    <t>14005.79</t>
+    <t>14081.38</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C624"/>
+  <dimension ref="A1:C625"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7247,10 +7247,21 @@
       <c r="A624" s="2">
         <v>46276</v>
       </c>
-      <c r="B624" t="s">
+      <c r="B624">
+        <v>106500</v>
+      </c>
+      <c r="C624">
+        <v>14005.79</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3">
+      <c r="A625" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B625" t="s">
         <v>3</v>
       </c>
-      <c r="C624" t="s">
+      <c r="C625" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>107000</t>
   </si>
   <si>
-    <t>14081.38</t>
+    <t>14078.66</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C625"/>
+  <dimension ref="A1:C626"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7258,10 +7258,21 @@
       <c r="A625" s="2">
         <v>46279</v>
       </c>
-      <c r="B625" t="s">
+      <c r="B625">
+        <v>107000</v>
+      </c>
+      <c r="C625">
+        <v>14081.38</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3">
+      <c r="A626" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B626" t="s">
         <v>3</v>
       </c>
-      <c r="C625" t="s">
+      <c r="C626" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>107000</t>
   </si>
   <si>
-    <t>14078.66</t>
+    <t>14074.27</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C626"/>
+  <dimension ref="A1:C627"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7269,10 +7269,21 @@
       <c r="A626" s="2">
         <v>46280</v>
       </c>
-      <c r="B626" t="s">
+      <c r="B626">
+        <v>107000</v>
+      </c>
+      <c r="C626">
+        <v>14078.66</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3">
+      <c r="A627" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B627" t="s">
         <v>3</v>
       </c>
-      <c r="C626" t="s">
+      <c r="C627" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>107000</t>
   </si>
   <si>
-    <t>14074.27</t>
+    <t>14085.36</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C627"/>
+  <dimension ref="A1:C628"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7280,10 +7280,21 @@
       <c r="A627" s="2">
         <v>46281</v>
       </c>
-      <c r="B627" t="s">
+      <c r="B627">
+        <v>107000</v>
+      </c>
+      <c r="C627">
+        <v>14074.27</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3">
+      <c r="A628" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B628" t="s">
         <v>3</v>
       </c>
-      <c r="C627" t="s">
+      <c r="C628" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>107000</t>
   </si>
   <si>
-    <t>14085.36</t>
+    <t>14084.11</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C628"/>
+  <dimension ref="A1:C629"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7291,10 +7291,21 @@
       <c r="A628" s="2">
         <v>46282</v>
       </c>
-      <c r="B628" t="s">
+      <c r="B628">
+        <v>107000</v>
+      </c>
+      <c r="C628">
+        <v>14085.36</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3">
+      <c r="A629" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B629" t="s">
         <v>3</v>
       </c>
-      <c r="C628" t="s">
+      <c r="C629" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>107000</t>
   </si>
   <si>
-    <t>14084.11</t>
+    <t>14097.74</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C629"/>
+  <dimension ref="A1:C630"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7302,10 +7302,21 @@
       <c r="A629" s="2">
         <v>46283</v>
       </c>
-      <c r="B629" t="s">
+      <c r="B629">
+        <v>107000</v>
+      </c>
+      <c r="C629">
+        <v>14084.11</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3">
+      <c r="A630" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B630" t="s">
         <v>3</v>
       </c>
-      <c r="C629" t="s">
+      <c r="C630" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>107000</t>
   </si>
   <si>
-    <t>14097.74</t>
+    <t>14108.45</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C630"/>
+  <dimension ref="A1:C631"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7313,10 +7313,21 @@
       <c r="A630" s="2">
         <v>46286</v>
       </c>
-      <c r="B630" t="s">
+      <c r="B630">
+        <v>107000</v>
+      </c>
+      <c r="C630">
+        <v>14097.74</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3">
+      <c r="A631" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B631" t="s">
         <v>3</v>
       </c>
-      <c r="C630" t="s">
+      <c r="C631" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>107000</t>
   </si>
   <si>
-    <t>14108.45</t>
+    <t>14098.79</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C631"/>
+  <dimension ref="A1:C632"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7324,10 +7324,21 @@
       <c r="A631" s="2">
         <v>46287</v>
       </c>
-      <c r="B631" t="s">
+      <c r="B631">
+        <v>107000</v>
+      </c>
+      <c r="C631">
+        <v>14108.45</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3">
+      <c r="A632" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B632" t="s">
         <v>3</v>
       </c>
-      <c r="C631" t="s">
+      <c r="C632" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>107000</t>
   </si>
   <si>
-    <t>14098.79</t>
+    <t>14071.34</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C632"/>
+  <dimension ref="A1:C633"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7335,10 +7335,21 @@
       <c r="A632" s="2">
         <v>46288</v>
       </c>
-      <c r="B632" t="s">
+      <c r="B632">
+        <v>107000</v>
+      </c>
+      <c r="C632">
+        <v>14098.79</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3">
+      <c r="A633" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B633" t="s">
         <v>3</v>
       </c>
-      <c r="C632" t="s">
+      <c r="C633" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>107000</t>
   </si>
   <si>
-    <t>14071.34</t>
+    <t>14065.28</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C633"/>
+  <dimension ref="A1:C634"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7346,10 +7346,21 @@
       <c r="A633" s="2">
         <v>46289</v>
       </c>
-      <c r="B633" t="s">
+      <c r="B633">
+        <v>107000</v>
+      </c>
+      <c r="C633">
+        <v>14071.34</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3">
+      <c r="A634" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B634" t="s">
         <v>3</v>
       </c>
-      <c r="C633" t="s">
+      <c r="C634" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>107000</t>
   </si>
   <si>
-    <t>14065.28</t>
+    <t>14075.11</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C634"/>
+  <dimension ref="A1:C635"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7357,10 +7357,21 @@
       <c r="A634" s="2">
         <v>46293</v>
       </c>
-      <c r="B634" t="s">
+      <c r="B634">
+        <v>107000</v>
+      </c>
+      <c r="C634">
+        <v>14065.28</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3">
+      <c r="A635" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B635" t="s">
         <v>3</v>
       </c>
-      <c r="C634" t="s">
+      <c r="C635" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>107000</t>
   </si>
   <si>
-    <t>14075.11</t>
+    <t>14078.87</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C635"/>
+  <dimension ref="A1:C636"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7368,10 +7368,21 @@
       <c r="A635" s="2">
         <v>46294</v>
       </c>
-      <c r="B635" t="s">
+      <c r="B635">
+        <v>107000</v>
+      </c>
+      <c r="C635">
+        <v>14075.11</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3">
+      <c r="A636" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B636" t="s">
         <v>3</v>
       </c>
-      <c r="C635" t="s">
+      <c r="C636" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>107000</t>
   </si>
   <si>
-    <t>14078.87</t>
+    <t>14078.45</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C636"/>
+  <dimension ref="A1:C637"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7379,10 +7379,21 @@
       <c r="A636" s="2">
         <v>46295</v>
       </c>
-      <c r="B636" t="s">
+      <c r="B636">
+        <v>107000</v>
+      </c>
+      <c r="C636">
+        <v>14078.87</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3">
+      <c r="A637" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B637" t="s">
         <v>3</v>
       </c>
-      <c r="C636" t="s">
+      <c r="C637" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>107000</t>
   </si>
   <si>
-    <t>14078.45</t>
+    <t>14086.62</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C637"/>
+  <dimension ref="A1:C638"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7390,10 +7390,21 @@
       <c r="A637" s="2">
         <v>46303</v>
       </c>
-      <c r="B637" t="s">
+      <c r="B637">
+        <v>107000</v>
+      </c>
+      <c r="C637">
+        <v>14078.45</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3">
+      <c r="A638" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B638" t="s">
         <v>3</v>
       </c>
-      <c r="C637" t="s">
+      <c r="C638" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -25,10 +25,10 @@
     <t>Avg With Rate(USD/mt,VAT included)</t>
   </si>
   <si>
-    <t>107000</t>
+    <t>104000</t>
   </si>
   <si>
-    <t>14086.62</t>
+    <t>13715.95</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C638"/>
+  <dimension ref="A1:C639"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7401,10 +7401,21 @@
       <c r="A638" s="2">
         <v>46304</v>
       </c>
-      <c r="B638" t="s">
+      <c r="B638">
+        <v>107000</v>
+      </c>
+      <c r="C638">
+        <v>14086.62</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3">
+      <c r="A639" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B639" t="s">
         <v>3</v>
       </c>
-      <c r="C638" t="s">
+      <c r="C639" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -25,10 +25,10 @@
     <t>Avg With Rate(USD/mt,VAT included)</t>
   </si>
   <si>
-    <t>104000</t>
+    <t>100000</t>
   </si>
   <si>
-    <t>13715.95</t>
+    <t>13188.22</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C639"/>
+  <dimension ref="A1:C640"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7412,10 +7412,21 @@
       <c r="A639" s="2">
         <v>46307</v>
       </c>
-      <c r="B639" t="s">
+      <c r="B639">
+        <v>104000</v>
+      </c>
+      <c r="C639">
+        <v>13715.95</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3">
+      <c r="A640" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B640" t="s">
         <v>3</v>
       </c>
-      <c r="C639" t="s">
+      <c r="C640" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -25,10 +25,10 @@
     <t>Avg With Rate(USD/mt,VAT included)</t>
   </si>
   <si>
-    <t>100000</t>
+    <t>97000</t>
   </si>
   <si>
-    <t>13188.22</t>
+    <t>12795.05</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C640"/>
+  <dimension ref="A1:C641"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7423,10 +7423,21 @@
       <c r="A640" s="2">
         <v>46308</v>
       </c>
-      <c r="B640" t="s">
+      <c r="B640">
+        <v>100000</v>
+      </c>
+      <c r="C640">
+        <v>13188.22</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3">
+      <c r="A641" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B641" t="s">
         <v>3</v>
       </c>
-      <c r="C640" t="s">
+      <c r="C641" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>97000</t>
   </si>
   <si>
-    <t>12795.05</t>
+    <t>12783.81</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C641"/>
+  <dimension ref="A1:C642"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7434,10 +7434,21 @@
       <c r="A641" s="2">
         <v>46309</v>
       </c>
-      <c r="B641" t="s">
+      <c r="B641">
+        <v>97000</v>
+      </c>
+      <c r="C641">
+        <v>12795.05</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3">
+      <c r="A642" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B642" t="s">
         <v>3</v>
       </c>
-      <c r="C641" t="s">
+      <c r="C642" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -25,10 +25,10 @@
     <t>Avg With Rate(USD/mt,VAT included)</t>
   </si>
   <si>
-    <t>97000</t>
+    <t>94000</t>
   </si>
   <si>
-    <t>12783.81</t>
+    <t>12400.07</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C642"/>
+  <dimension ref="A1:C643"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7445,10 +7445,21 @@
       <c r="A642" s="2">
         <v>46310</v>
       </c>
-      <c r="B642" t="s">
+      <c r="B642">
+        <v>97000</v>
+      </c>
+      <c r="C642">
+        <v>12783.81</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3">
+      <c r="A643" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B643" t="s">
         <v>3</v>
       </c>
-      <c r="C642" t="s">
+      <c r="C643" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -25,10 +25,10 @@
     <t>Avg With Rate(USD/mt,VAT included)</t>
   </si>
   <si>
-    <t>94000</t>
+    <t>92000</t>
   </si>
   <si>
-    <t>12400.07</t>
+    <t>12145.11</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C643"/>
+  <dimension ref="A1:C644"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7456,10 +7456,21 @@
       <c r="A643" s="2">
         <v>46311</v>
       </c>
-      <c r="B643" t="s">
+      <c r="B643">
+        <v>94000</v>
+      </c>
+      <c r="C643">
+        <v>12400.07</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3">
+      <c r="A644" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B644" t="s">
         <v>3</v>
       </c>
-      <c r="C643" t="s">
+      <c r="C644" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>92000</t>
   </si>
   <si>
-    <t>12145.11</t>
+    <t>12155.99</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C644"/>
+  <dimension ref="A1:C645"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7467,10 +7467,21 @@
       <c r="A644" s="2">
         <v>46314</v>
       </c>
-      <c r="B644" t="s">
+      <c r="B644">
+        <v>92000</v>
+      </c>
+      <c r="C644">
+        <v>12145.11</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3">
+      <c r="A645" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B645" t="s">
         <v>3</v>
       </c>
-      <c r="C644" t="s">
+      <c r="C645" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>92000</t>
   </si>
   <si>
-    <t>12155.99</t>
+    <t>12161.61</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C645"/>
+  <dimension ref="A1:C646"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7478,10 +7478,21 @@
       <c r="A645" s="2">
         <v>46315</v>
       </c>
-      <c r="B645" t="s">
+      <c r="B645">
+        <v>92000</v>
+      </c>
+      <c r="C645">
+        <v>12155.99</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3">
+      <c r="A646" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B646" t="s">
         <v>3</v>
       </c>
-      <c r="C645" t="s">
+      <c r="C646" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>92000</t>
   </si>
   <si>
-    <t>12161.61</t>
+    <t>12165.61</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C646"/>
+  <dimension ref="A1:C647"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7489,10 +7489,21 @@
       <c r="A646" s="2">
         <v>46316</v>
       </c>
-      <c r="B646" t="s">
+      <c r="B646">
+        <v>92000</v>
+      </c>
+      <c r="C646">
+        <v>12161.61</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3">
+      <c r="A647" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B647" t="s">
         <v>3</v>
       </c>
-      <c r="C646" t="s">
+      <c r="C647" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>92000</t>
   </si>
   <si>
-    <t>12165.61</t>
+    <t>12165.98</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C647"/>
+  <dimension ref="A1:C648"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7500,10 +7500,21 @@
       <c r="A647" s="2">
         <v>46317</v>
       </c>
-      <c r="B647" t="s">
+      <c r="B647">
+        <v>92000</v>
+      </c>
+      <c r="C647">
+        <v>12165.61</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3">
+      <c r="A648" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B648" t="s">
         <v>3</v>
       </c>
-      <c r="C647" t="s">
+      <c r="C648" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>92000</t>
   </si>
   <si>
-    <t>12165.98</t>
+    <t>12174.16</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C648"/>
+  <dimension ref="A1:C649"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7511,10 +7511,21 @@
       <c r="A648" s="2">
         <v>46318</v>
       </c>
-      <c r="B648" t="s">
+      <c r="B648">
+        <v>92000</v>
+      </c>
+      <c r="C648">
+        <v>12165.98</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3">
+      <c r="A649" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B649" t="s">
         <v>3</v>
       </c>
-      <c r="C648" t="s">
+      <c r="C649" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>92000</t>
   </si>
   <si>
-    <t>12174.16</t>
+    <t>12175.98</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C649"/>
+  <dimension ref="A1:C650"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7522,10 +7522,21 @@
       <c r="A649" s="2">
         <v>46321</v>
       </c>
-      <c r="B649" t="s">
+      <c r="B649">
+        <v>92000</v>
+      </c>
+      <c r="C649">
+        <v>12174.16</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3">
+      <c r="A650" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B650" t="s">
         <v>3</v>
       </c>
-      <c r="C649" t="s">
+      <c r="C650" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>92000</t>
   </si>
   <si>
-    <t>12175.98</t>
+    <t>12182.72</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C650"/>
+  <dimension ref="A1:C651"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7533,10 +7533,21 @@
       <c r="A650" s="2">
         <v>46322</v>
       </c>
-      <c r="B650" t="s">
+      <c r="B650">
+        <v>92000</v>
+      </c>
+      <c r="C650">
+        <v>12175.98</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3">
+      <c r="A651" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B651" t="s">
         <v>3</v>
       </c>
-      <c r="C650" t="s">
+      <c r="C651" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>92000</t>
   </si>
   <si>
-    <t>12182.72</t>
+    <t>12183.27</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C651"/>
+  <dimension ref="A1:C652"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7544,10 +7544,21 @@
       <c r="A651" s="2">
         <v>46323</v>
       </c>
-      <c r="B651" t="s">
+      <c r="B651">
+        <v>92000</v>
+      </c>
+      <c r="C651">
+        <v>12182.72</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3">
+      <c r="A652" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B652" t="s">
         <v>3</v>
       </c>
-      <c r="C651" t="s">
+      <c r="C652" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>92000</t>
   </si>
   <si>
-    <t>12183.27</t>
+    <t>12190.93</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C652"/>
+  <dimension ref="A1:C653"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7555,10 +7555,21 @@
       <c r="A652" s="2">
         <v>46324</v>
       </c>
-      <c r="B652" t="s">
+      <c r="B652">
+        <v>92000</v>
+      </c>
+      <c r="C652">
+        <v>12183.27</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3">
+      <c r="A653" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B653" t="s">
         <v>3</v>
       </c>
-      <c r="C652" t="s">
+      <c r="C653" t="s">
         <v>4</v>
       </c>
     </row>
